--- a/data/raw/genie_industriel.xlsx
+++ b/data/raw/genie_industriel.xlsx
@@ -1015,7 +1015,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="26" min="1" max="1"/>
@@ -1769,68 +1769,68 @@
         <v>0</v>
       </c>
       <c r="E10" s="45" t="n">
-        <v>12.08</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="F10" s="45" t="n">
-        <v>13.02</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="G10" s="45" t="n">
-        <v>17.81</v>
+        <v>14.06</v>
       </c>
       <c r="H10" s="45" t="n">
-        <v>18.28</v>
+        <v>14.49</v>
       </c>
       <c r="I10" s="44" t="n">
-        <v>9.06</v>
+        <v>6.16</v>
       </c>
       <c r="J10" s="45" t="n">
-        <v>12.65</v>
+        <v>10.75</v>
       </c>
       <c r="K10" s="44" t="n">
-        <v>11.88</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="M10" s="68" t="n">
-        <v>13.71</v>
+        <v>10.2</v>
       </c>
       <c r="N10" s="43" t="n">
         <v>2</v>
       </c>
       <c r="O10" s="45" t="n">
-        <v>18.58</v>
+        <v>15.71</v>
       </c>
       <c r="P10" s="45" t="n">
-        <v>16.81</v>
+        <v>12.31</v>
       </c>
       <c r="Q10" s="44" t="n">
-        <v>10.57</v>
+        <v>6.94</v>
       </c>
       <c r="R10" s="45" t="n">
-        <v>15.71</v>
+        <v>11.3</v>
       </c>
       <c r="S10" s="45" t="n">
-        <v>16.13</v>
+        <v>12.53</v>
       </c>
       <c r="T10" s="45" t="n">
-        <v>16.79</v>
+        <v>13.2</v>
       </c>
       <c r="U10" s="45" t="n">
-        <v>15.27</v>
+        <v>11.55</v>
       </c>
       <c r="V10" s="47" t="n">
-        <v>13.08</v>
+        <v>9.67</v>
       </c>
       <c r="W10" s="68" t="n">
-        <v>15.26</v>
+        <v>11.65</v>
       </c>
       <c r="X10" s="70" t="n">
-        <v>14.48</v>
+        <v>10.93</v>
       </c>
       <c r="Y10" s="63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z10" s="80" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -2534,68 +2534,68 @@
         <v>6</v>
       </c>
       <c r="E19" s="44" t="n">
-        <v>10.04</v>
+        <v>7.64</v>
       </c>
       <c r="F19" s="45" t="n">
-        <v>15.71</v>
+        <v>12.07</v>
       </c>
       <c r="G19" s="44" t="n">
-        <v>10.77</v>
+        <v>7.17</v>
       </c>
       <c r="H19" s="45" t="n">
-        <v>15.55</v>
+        <v>11.26</v>
       </c>
       <c r="I19" s="45" t="n">
-        <v>17.07</v>
+        <v>11.92</v>
       </c>
       <c r="J19" s="45" t="n">
-        <v>16.95</v>
+        <v>13.74</v>
       </c>
       <c r="K19" s="45" t="n">
-        <v>14.07</v>
+        <v>10.47</v>
       </c>
       <c r="M19" s="68" t="n">
-        <v>14</v>
+        <v>10.61</v>
       </c>
       <c r="N19" s="43" t="n">
         <v>2</v>
       </c>
       <c r="O19" s="45" t="n">
-        <v>13.15</v>
+        <v>11.13</v>
       </c>
       <c r="P19" s="45" t="n">
-        <v>13.66</v>
+        <v>9.970000000000001</v>
       </c>
       <c r="Q19" s="45" t="n">
-        <v>15.27</v>
+        <v>12.42</v>
       </c>
       <c r="R19" s="44" t="n">
-        <v>7.86</v>
+        <v>6.36</v>
       </c>
       <c r="S19" s="45" t="n">
-        <v>15.09</v>
+        <v>10.26</v>
       </c>
       <c r="T19" s="45" t="n">
-        <v>13.36</v>
+        <v>10.04</v>
       </c>
       <c r="U19" s="45" t="n">
-        <v>12.25</v>
+        <v>9.67</v>
       </c>
       <c r="V19" s="47" t="n">
-        <v>13.13</v>
+        <v>10.79</v>
       </c>
       <c r="W19" s="68" t="n">
-        <v>13.08</v>
+        <v>10.08</v>
       </c>
       <c r="X19" s="70" t="n">
-        <v>13.54</v>
+        <v>10.34</v>
       </c>
       <c r="Y19" s="63" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Z19" s="80" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -3044,68 +3044,68 @@
         <v>16</v>
       </c>
       <c r="E25" s="45" t="n">
-        <v>19.25</v>
+        <v>13.77</v>
       </c>
       <c r="F25" s="45" t="n">
-        <v>12.97</v>
+        <v>9</v>
       </c>
       <c r="G25" s="45" t="n">
-        <v>13.89</v>
+        <v>11</v>
       </c>
       <c r="H25" s="44" t="n">
-        <v>11.79</v>
+        <v>9.57</v>
       </c>
       <c r="I25" s="45" t="n">
-        <v>18.52</v>
+        <v>13.33</v>
       </c>
       <c r="J25" s="45" t="n">
-        <v>13.35</v>
+        <v>8.93</v>
       </c>
       <c r="K25" s="45" t="n">
-        <v>17.99</v>
+        <v>15.08</v>
       </c>
       <c r="M25" s="68" t="n">
-        <v>15.37</v>
+        <v>11.53</v>
       </c>
       <c r="N25" s="43" t="n">
         <v>8</v>
       </c>
       <c r="O25" s="45" t="n">
-        <v>17.8</v>
+        <v>12.99</v>
       </c>
       <c r="P25" s="44" t="n">
-        <v>10.45</v>
+        <v>7.87</v>
       </c>
       <c r="Q25" s="45" t="n">
-        <v>16.88</v>
+        <v>13.8</v>
       </c>
       <c r="R25" s="45" t="n">
-        <v>12.19</v>
+        <v>9.57</v>
       </c>
       <c r="S25" s="45" t="n">
-        <v>18.68</v>
+        <v>14.89</v>
       </c>
       <c r="T25" s="45" t="n">
-        <v>13.35</v>
+        <v>9.24</v>
       </c>
       <c r="U25" s="45" t="n">
-        <v>17.26</v>
+        <v>13.09</v>
       </c>
       <c r="V25" s="44" t="n">
-        <v>10.54</v>
+        <v>8.32</v>
       </c>
       <c r="W25" s="68" t="n">
-        <v>14.52</v>
+        <v>11.22</v>
       </c>
       <c r="X25" s="70" t="n">
-        <v>14.95</v>
+        <v>11.38</v>
       </c>
       <c r="Y25" s="63" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Z25" s="80" t="inlineStr">
         <is>
-          <t>Non</t>
+          <t>Oui</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="N2:W2"/>
@@ -4320,7 +4319,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Z40"/>
+  <dimension ref="A1:Z39"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="10" customWidth="1" style="26" min="1" max="1"/>
@@ -7604,7 +7603,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="N2:W2"/>
